--- a/sample_data/wedstrijd-data-2026-08-29.xlsx
+++ b/sample_data/wedstrijd-data-2026-08-29.xlsx
@@ -1372,10 +1372,10 @@
         <v>9</v>
       </c>
       <c r="C16" t="n">
-        <v>311.586718</v>
+        <v>337.472931</v>
       </c>
       <c r="D16" t="n">
-        <v>268.349682</v>
+        <v>285.077162</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -1519,10 +1519,10 @@
         <v>3</v>
       </c>
       <c r="C23" t="n">
-        <v>251.439194</v>
+        <v>205.083637</v>
       </c>
       <c r="D23" t="n">
-        <v>244.766889</v>
+        <v>242.530592</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -1708,10 +1708,10 @@
         <v>4</v>
       </c>
       <c r="C32" t="n">
-        <v>317.264639</v>
+        <v>342.026528</v>
       </c>
       <c r="D32" t="n">
-        <v>226.8592</v>
+        <v>215.088018</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -1876,10 +1876,10 @@
         <v>8</v>
       </c>
       <c r="C40" t="n">
-        <v>257.342091</v>
+        <v>256.665084</v>
       </c>
       <c r="D40" t="n">
-        <v>312.76925</v>
+        <v>315.068743</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>

--- a/sample_data/wedstrijd-data-2026-08-29.xlsx
+++ b/sample_data/wedstrijd-data-2026-08-29.xlsx
@@ -1078,10 +1078,10 @@
         <v>2</v>
       </c>
       <c r="C2" t="n">
-        <v>405.507863</v>
+        <v>455.561606</v>
       </c>
       <c r="D2" t="n">
-        <v>132.191883</v>
+        <v>148.783869</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -1099,10 +1099,10 @@
         <v>7</v>
       </c>
       <c r="C3" t="n">
-        <v>369.385213</v>
+        <v>414.980168</v>
       </c>
       <c r="D3" t="n">
-        <v>180.071056</v>
+        <v>202.672567</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -1120,10 +1120,10 @@
         <v>1</v>
       </c>
       <c r="C4" t="n">
-        <v>72.281069</v>
+        <v>81.20306100000001</v>
       </c>
       <c r="D4" t="n">
-        <v>337.652459</v>
+        <v>380.032705</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -1141,10 +1141,10 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>345.868726</v>
+        <v>388.56093</v>
       </c>
       <c r="D5" t="n">
-        <v>303.972858</v>
+        <v>342.12583</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -1162,10 +1162,10 @@
         <v>1</v>
       </c>
       <c r="C6" t="n">
-        <v>182.581656</v>
+        <v>205.118569</v>
       </c>
       <c r="D6" t="n">
-        <v>323.842667</v>
+        <v>364.489586</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -1183,10 +1183,10 @@
         <v>7</v>
       </c>
       <c r="C7" t="n">
-        <v>197.447108</v>
+        <v>221.818933</v>
       </c>
       <c r="D7" t="n">
-        <v>191.235917</v>
+        <v>215.238779</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -1204,10 +1204,10 @@
         <v>1</v>
       </c>
       <c r="C8" t="n">
-        <v>418.946617</v>
+        <v>470.659169</v>
       </c>
       <c r="D8" t="n">
-        <v>301.740282</v>
+        <v>339.613033</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -1225,10 +1225,10 @@
         <v>7</v>
       </c>
       <c r="C9" t="n">
-        <v>105.837685</v>
+        <v>118.901728</v>
       </c>
       <c r="D9" t="n">
-        <v>195.052529</v>
+        <v>219.53443</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -1246,10 +1246,10 @@
         <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>84.091702</v>
+        <v>94.471536</v>
       </c>
       <c r="D10" t="n">
-        <v>123.59459</v>
+        <v>139.107491</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -1267,10 +1267,10 @@
         <v>2</v>
       </c>
       <c r="C11" t="n">
-        <v>130.201388</v>
+        <v>146.272758</v>
       </c>
       <c r="D11" t="n">
-        <v>284.395306</v>
+        <v>320.091013</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -1288,10 +1288,10 @@
         <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>135.235476</v>
+        <v>151.928227</v>
       </c>
       <c r="D12" t="n">
-        <v>182.331723</v>
+        <v>205.21698</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -1309,10 +1309,10 @@
         <v>5</v>
       </c>
       <c r="C13" t="n">
-        <v>436.790938</v>
+        <v>490.706098</v>
       </c>
       <c r="D13" t="n">
-        <v>285.349164</v>
+        <v>321.164594</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -1330,10 +1330,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>98.31276699999999</v>
+        <v>110.447974</v>
       </c>
       <c r="D14" t="n">
-        <v>224.095144</v>
+        <v>252.222313</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -1351,10 +1351,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>429.490924</v>
+        <v>482.50501</v>
       </c>
       <c r="D15" t="n">
-        <v>328.399789</v>
+        <v>369.618692</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -1372,10 +1372,10 @@
         <v>9</v>
       </c>
       <c r="C16" t="n">
-        <v>337.472931</v>
+        <v>379.128803</v>
       </c>
       <c r="D16" t="n">
-        <v>285.077162</v>
+        <v>320.858452</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -1393,10 +1393,10 @@
         <v>1</v>
       </c>
       <c r="C17" t="n">
-        <v>313.147907</v>
+        <v>351.801227</v>
       </c>
       <c r="D17" t="n">
-        <v>115.72343</v>
+        <v>130.248387</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -1414,10 +1414,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>67.22793799999999</v>
+        <v>75.52619900000001</v>
       </c>
       <c r="D18" t="n">
-        <v>149.075738</v>
+        <v>167.78689</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -1435,10 +1435,10 @@
         <v>4</v>
       </c>
       <c r="C19" t="n">
-        <v>219.524538</v>
+        <v>246.621484</v>
       </c>
       <c r="D19" t="n">
-        <v>197.205638</v>
+        <v>221.957786</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -1456,10 +1456,10 @@
         <v>1</v>
       </c>
       <c r="C20" t="n">
-        <v>401.468572</v>
+        <v>451.023727</v>
       </c>
       <c r="D20" t="n">
-        <v>197.942668</v>
+        <v>222.787324</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -1477,10 +1477,10 @@
         <v>4</v>
       </c>
       <c r="C21" t="n">
-        <v>353.797608</v>
+        <v>397.468511</v>
       </c>
       <c r="D21" t="n">
-        <v>112.941672</v>
+        <v>127.117478</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -1498,10 +1498,10 @@
         <v>3</v>
       </c>
       <c r="C22" t="n">
-        <v>86.561193</v>
+        <v>97.245848</v>
       </c>
       <c r="D22" t="n">
-        <v>172.388774</v>
+        <v>194.026049</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -1519,10 +1519,10 @@
         <v>3</v>
       </c>
       <c r="C23" t="n">
-        <v>205.083637</v>
+        <v>230.398076</v>
       </c>
       <c r="D23" t="n">
-        <v>242.530592</v>
+        <v>272.971674</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -1540,10 +1540,10 @@
         <v>7</v>
       </c>
       <c r="C24" t="n">
-        <v>453.226556</v>
+        <v>509.170443</v>
       </c>
       <c r="D24" t="n">
-        <v>316.113655</v>
+        <v>355.790472</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -1561,10 +1561,10 @@
         <v>1</v>
       </c>
       <c r="C25" t="n">
-        <v>380.697572</v>
+        <v>427.688864</v>
       </c>
       <c r="D25" t="n">
-        <v>238.895595</v>
+        <v>268.880433</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -1582,10 +1582,10 @@
         <v>2</v>
       </c>
       <c r="C26" t="n">
-        <v>292.292815</v>
+        <v>328.371892</v>
       </c>
       <c r="D26" t="n">
-        <v>334.952619</v>
+        <v>376.993997</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -1603,10 +1603,10 @@
         <v>3</v>
       </c>
       <c r="C27" t="n">
-        <v>212.624842</v>
+        <v>238.870127</v>
       </c>
       <c r="D27" t="n">
-        <v>295.695507</v>
+        <v>332.809552</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -1624,10 +1624,10 @@
         <v>2</v>
       </c>
       <c r="C28" t="n">
-        <v>91.61503500000001</v>
+        <v>102.92351</v>
       </c>
       <c r="D28" t="n">
-        <v>140.73013</v>
+        <v>158.393789</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -1645,10 +1645,10 @@
         <v>1</v>
       </c>
       <c r="C29" t="n">
-        <v>467.309986</v>
+        <v>524.992256</v>
       </c>
       <c r="D29" t="n">
-        <v>257.718984</v>
+        <v>290.066429</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -1666,10 +1666,10 @@
         <v>2</v>
       </c>
       <c r="C30" t="n">
-        <v>152.651222</v>
+        <v>171.493681</v>
       </c>
       <c r="D30" t="n">
-        <v>248.95051</v>
+        <v>280.197385</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -1687,10 +1687,10 @@
         <v>9</v>
       </c>
       <c r="C31" t="n">
-        <v>178.402072</v>
+        <v>200.423079</v>
       </c>
       <c r="D31" t="n">
-        <v>321.517307</v>
+        <v>361.87236</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -1708,10 +1708,10 @@
         <v>4</v>
       </c>
       <c r="C32" t="n">
-        <v>342.026528</v>
+        <v>384.244472</v>
       </c>
       <c r="D32" t="n">
-        <v>215.088018</v>
+        <v>242.084663</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -1729,10 +1729,10 @@
         <v>1</v>
       </c>
       <c r="C33" t="n">
-        <v>175.816302</v>
+        <v>197.518135</v>
       </c>
       <c r="D33" t="n">
-        <v>130.250438</v>
+        <v>146.598745</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -1750,10 +1750,10 @@
         <v>4</v>
       </c>
       <c r="C34" t="n">
-        <v>255.122209</v>
+        <v>286.613144</v>
       </c>
       <c r="D34" t="n">
-        <v>143.627518</v>
+        <v>161.654841</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -1771,10 +1771,10 @@
         <v>2</v>
       </c>
       <c r="C35" t="n">
-        <v>159.168122</v>
+        <v>178.814992</v>
       </c>
       <c r="D35" t="n">
-        <v>168.689003</v>
+        <v>189.861903</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -1792,10 +1792,10 @@
         <v>5</v>
       </c>
       <c r="C36" t="n">
-        <v>87.210295</v>
+        <v>97.975072</v>
       </c>
       <c r="D36" t="n">
-        <v>307.804788</v>
+        <v>346.438723</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -1813,10 +1813,10 @@
         <v>8</v>
       </c>
       <c r="C37" t="n">
-        <v>110.292217</v>
+        <v>123.906104</v>
       </c>
       <c r="D37" t="n">
-        <v>317.489343</v>
+        <v>357.338828</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -1834,10 +1834,10 @@
         <v>5</v>
       </c>
       <c r="C38" t="n">
-        <v>329.432267</v>
+        <v>370.095641</v>
       </c>
       <c r="D38" t="n">
-        <v>188.509526</v>
+        <v>212.170186</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -1855,10 +1855,10 @@
         <v>5</v>
       </c>
       <c r="C39" t="n">
-        <v>69.45570600000001</v>
+        <v>78.02895100000001</v>
       </c>
       <c r="D39" t="n">
-        <v>205.023942</v>
+        <v>230.757399</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -1876,10 +1876,10 @@
         <v>8</v>
       </c>
       <c r="C40" t="n">
-        <v>256.665084</v>
+        <v>288.346463</v>
       </c>
       <c r="D40" t="n">
-        <v>315.068743</v>
+        <v>354.614408</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
@@ -1897,10 +1897,10 @@
         <v>4</v>
       </c>
       <c r="C41" t="n">
-        <v>340.482357</v>
+        <v>382.509696</v>
       </c>
       <c r="D41" t="n">
-        <v>119.566996</v>
+        <v>134.574376</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -1918,10 +1918,10 @@
         <v>5</v>
       </c>
       <c r="C42" t="n">
-        <v>357.423414</v>
+        <v>401.541867</v>
       </c>
       <c r="D42" t="n">
-        <v>241.927479</v>
+        <v>272.292862</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
@@ -1939,10 +1939,10 @@
         <v>3</v>
       </c>
       <c r="C43" t="n">
-        <v>430.821425</v>
+        <v>483.99974</v>
       </c>
       <c r="D43" t="n">
-        <v>121.622839</v>
+        <v>136.888257</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
@@ -1960,10 +1960,10 @@
         <v>7</v>
       </c>
       <c r="C44" t="n">
-        <v>474.853143</v>
+        <v>533.466501</v>
       </c>
       <c r="D44" t="n">
-        <v>264.292929</v>
+        <v>297.465498</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
@@ -1981,10 +1981,10 @@
         <v>8</v>
       </c>
       <c r="C45" t="n">
-        <v>438.553721</v>
+        <v>492.686471</v>
       </c>
       <c r="D45" t="n">
-        <v>261.247514</v>
+        <v>294.03784</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
